--- a/tests/fixtures/acme/sources/taxonomies/product-category.xlsx
+++ b/tests/fixtures/acme/sources/taxonomies/product-category.xlsx
@@ -467,7 +467,11 @@
           <t>Reference Entity UUID</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>8f4b1bf5-8ec7-465b-8e0f-c221d260a34c</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>sem:enumerates</t>
@@ -706,8 +710,6 @@
           <t>"Tools"@en</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Implements used to work material by hand or by power.</t>
@@ -765,7 +767,6 @@
           <t>"Power tools"@en</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Tools driven by an electric motor or compressed air.</t>
@@ -776,10 +777,6 @@
           <t>Powered tools; Electric tools</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -837,7 +834,6 @@
           <t>Cordless drill, hammer drill</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -875,11 +871,6 @@
           <t>Power tools that abrade a surface smooth.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -907,7 +898,6 @@
           <t>"Hand tools"@en</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Tools worked entirely by hand.</t>
@@ -918,10 +908,6 @@
           <t>Manual tools</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -964,10 +950,6 @@
           <t>Wrenches</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -990,15 +972,11 @@
           <t>"Fasteners"@en</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Hardware that joins two things together.</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Excludes adhesives, which are consumables.</t>
@@ -1041,21 +1019,16 @@
           <t>"Screws"@en</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Threaded fasteners driven into material.</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Screwes</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -1067,20 +1040,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tests/fixtures/acme/sources/taxonomies/product-category.xlsx
+++ b/tests/fixtures/acme/sources/taxonomies/product-category.xlsx
@@ -710,6 +710,8 @@
           <t>"Tools"@en</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Implements used to work material by hand or by power.</t>
@@ -767,6 +769,7 @@
           <t>"Power tools"@en</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Tools driven by an electric motor or compressed air.</t>
@@ -777,6 +780,10 @@
           <t>Powered tools; Electric tools</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -801,7 +808,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>"Power tools"@en</t>
+          <t>"Power tools"@en</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -834,6 +841,7 @@
           <t>Cordless drill, hammer drill</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -848,7 +856,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ont:Sanders</t>
+          <t>ont:Sand­ers</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -868,9 +876,14 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Power tools that abrade a surface smooth.</t>
-        </is>
-      </c>
+          <t>Power tools that abrade a surface smooth.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -898,6 +911,7 @@
           <t>"Hand tools"@en</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Tools worked entirely by hand.</t>
@@ -908,6 +922,10 @@
           <t>Manual tools</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -950,6 +968,10 @@
           <t>Wrenches</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -972,11 +994,15 @@
           <t>"Fasteners"@en</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Hardware that joins two things together.</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>Excludes adhesives, which are consumables.</t>
@@ -1019,16 +1045,21 @@
           <t>"Screws"@en</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Threaded fasteners driven into material.</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>Screwes</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>PIM</t>
@@ -1040,7 +1071,20 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
